--- a/tests/realSuite/Basket-cadetti_e_Piano-viaggi_21-GENNAIO_2026_def-con-vettore/input.xlsx
+++ b/tests/realSuite/Basket-cadetti_e_Piano-viaggi_21-GENNAIO_2026_def-con-vettore/input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALDENO, Via Filzi, Fermata bus</t>
+          <t>1, Via della Torre Franca, Regole, Mattarello di Sopra, Mattarello, Trento, Territorio Val d'Adige, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38123, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -546,7 +546,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ROVERETO, Piazzale Orsi, Fermata bus CFP Veronesi</t>
+          <t>Scuola Elementare Regina Elena, 41, Via Dante Alighieri, Santa Maria, Rovereto, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38068, Italia</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/tests/realSuite/Basket-cadetti_e_Piano-viaggi_21-GENNAIO_2026_def-con-vettore/input.xlsx
+++ b/tests/realSuite/Basket-cadetti_e_Piano-viaggi_21-GENNAIO_2026_def-con-vettore/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO</t>
+          <t>IC ISERA-ROVERETO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1, Via della Torre Franca, Regole, Mattarello di Sopra, Mattarello, Trento, Territorio Val d'Adige, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38123, Italia</t>
+          <t>ROVERETO, Viale Della Vittoria, 43</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -451,135 +451,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC AVIO</t>
+          <t>IC MEZZANO SANTA CROCE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AVIO, Viale Degasperi, 69</t>
+          <t>MEZZANO, Via Molaren, 29</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ISERA-ROVERETO</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ROVERETO, Viale Della Vittoria, 43</t>
+          <t>SPORMAGGIORE, Via Alt Spaur, 5</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC MEZZANO SANTA CROCE</t>
+          <t>IC PRIMIERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEZZANO, Via Molaren, 29</t>
+          <t>FIERA DI PRIMIERO, Via Roma 2, Fermata bus</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC RIVA 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SPORMAGGIORE, Via Alt Spaur, 5</t>
+          <t>RIVA DEL GARDA, Viale Damiano Chiesa, 10, Fermata bus</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC PRIMIERO</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FIERA DI PRIMIERO, Via Roma 2, Fermata bus</t>
+          <t>Scuola Elementare Regina Elena, 41, Via Dante Alighieri, Santa Maria, Rovereto, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38068, Italia</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC RIVA 1</t>
+          <t>IC VALLE DEI LAGHI-DRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RIVA DEL GARDA, Viale Damiano Chiesa, 10, Fermata bus</t>
+          <t>CAVEDINE, Piazza Italia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IS GUETTI – Students Staff</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scuola Elementare Regina Elena, 41, Via Dante Alighieri, Santa Maria, Rovereto, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38068, Italia</t>
+          <t>TIONE, Via Durone, 53</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI-DRO</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CAVEDINE, Piazza Italia</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IS GUETTI – Students Staff</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TIONE, Via Durone, 53</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
         <v>8</v>
       </c>
     </row>
